--- a/tams-invest-parent/tams-invest-period/src/main/resources/tpl/TrdRepoDuration001.xlsx
+++ b/tams-invest-parent/tams-invest-period/src/main/resources/tpl/TrdRepoDuration001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22325"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\zgNoDEV2.1.2\tams-invest-parent\tams-invest-period\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-period\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA35E650-FEAD-441D-8FB1-DC255A08CD80}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>有效状态</t>
   </si>
@@ -59,10 +58,6 @@
   </si>
   <si>
     <t>到期结算金额</t>
-  </si>
-  <si>
-    <t>通道代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>实际结算金额</t>
@@ -76,7 +71,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -418,25 +413,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="5" width="19.25" customWidth="1"/>
-    <col min="6" max="7" width="17.375" customWidth="1"/>
-    <col min="8" max="8" width="16.75" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="12" width="10.875" customWidth="1"/>
-    <col min="13" max="13" width="12.875" customWidth="1"/>
-    <col min="14" max="14" width="13.375" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
-    <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.21875" customWidth="1"/>
+    <col min="5" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="11" width="10.88671875" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,40 +445,37 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
         <v>13</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
